--- a/output/Tables/Description/Walk/sex_proportion.xlsx
+++ b/output/Tables/Description/Walk/sex_proportion.xlsx
@@ -383,13 +383,13 @@
         </is>
       </c>
       <c r="B2">
-        <v>33441520.47565762</v>
+        <v>29117072.04661907</v>
       </c>
       <c r="C2">
-        <v>927312.5771707885</v>
+        <v>880408.1301945909</v>
       </c>
       <c r="D2">
-        <v>0.5547734504195798</v>
+        <v>0.5361666182034633</v>
       </c>
     </row>
     <row r="3">
@@ -399,13 +399,13 @@
         </is>
       </c>
       <c r="B3">
-        <v>26838077.35002333</v>
+        <v>25188942.27441757</v>
       </c>
       <c r="C3">
-        <v>896007.3640669049</v>
+        <v>876254.6758388366</v>
       </c>
       <c r="D3">
-        <v>0.4452265495804202</v>
+        <v>0.4638333817965365</v>
       </c>
     </row>
   </sheetData>

--- a/output/Tables/Description/Walk/sex_proportion.xlsx
+++ b/output/Tables/Description/Walk/sex_proportion.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D3"/>
+  <dimension ref="A1:F3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -372,6 +372,16 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>mean_km</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>mean_km_se</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>proportion</t>
         </is>
       </c>
@@ -389,6 +399,12 @@
         <v>880408.1301945909</v>
       </c>
       <c r="D2">
+        <v>1.193426722113971</v>
+      </c>
+      <c r="E2">
+        <v>0.03421506749649341</v>
+      </c>
+      <c r="F2">
         <v>0.5361666182034633</v>
       </c>
     </row>
@@ -405,6 +421,12 @@
         <v>876254.6758388366</v>
       </c>
       <c r="D3">
+        <v>1.125245065794931</v>
+      </c>
+      <c r="E3">
+        <v>0.03796516942271731</v>
+      </c>
+      <c r="F3">
         <v>0.4638333817965365</v>
       </c>
     </row>
